--- a/r_test/plot_metrics/Cluster_Summary.xlsx
+++ b/r_test/plot_metrics/Cluster_Summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -371,175 +371,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AN_TJ_1</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.74</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AN_TJ_2</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.72</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ATQ_VK_1</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.846938775510204</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BRW_PW_1</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.9054178145087236</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BRW_VS_1</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.9288194444444444</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_1</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0.675</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_2</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.9211111111111111</v>
-      </c>
-      <c r="C8">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_3</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0.8644444444444445</v>
-      </c>
-      <c r="C9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_4</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0.8311111111111111</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FRST_AK_2</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.66</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FRST_AK_3</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.775623268698061</v>
-      </c>
-      <c r="C12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PRUAIR_DW_1</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.8544</v>
-      </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PRUARC_DW_1</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>0.8941736028537456</v>
-      </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/r_test/plot_metrics/Cluster_Summary.xlsx
+++ b/r_test/plot_metrics/Cluster_Summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -371,6 +371,175 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AN_TJ_1</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.74</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AN_TJ_2</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.72</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ATQ_VK_1</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.846938775510204</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRW_PW_1</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.9054178145087236</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BRW_VS_1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.9288194444444444</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FLXTWRZONA_SD_1</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.675</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FLXTWRZONA_SD_2</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.9211111111111111</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FLXTWRZONA_SD_3</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.8644444444444445</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FLXTWRZONA_SD_4</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.8311111111111111</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FRST_AK_2</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.66</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FRST_AK_3</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.775623268698061</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PRUAIR_DW_1</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.8544</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PRUARC_DW_1</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.8941736028537456</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
